--- a/templates/EG_PromoCost.xlsx
+++ b/templates/EG_PromoCost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\OneDrive\Documents\EG America\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECD9AFA-F0D3-4A06-AC2C-16820ECAC7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3C811D-4A9E-46BB-AE93-BB5DE815C07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,13 +130,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="3">
     <numFmt numFmtId="165" formatCode="[$-10409]#,##0.0000;\-#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="[$-10409]m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="000000000000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -175,15 +174,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,12 +198,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
         <bgColor rgb="FFD3D3D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,11 +288,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -332,18 +317,8 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
@@ -363,9 +338,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -744,7 +727,7 @@
     <col min="3" max="3" width="27.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -753,116 +736,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="16"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="16"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="16"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="16"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -877,16 +860,16 @@
       <c r="D8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -901,32 +884,32 @@
       <c r="D9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="16"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -972,9 +955,8 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
@@ -986,9 +968,8 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -1000,9 +981,8 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
       <c r="I14" s="2"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -1014,9 +994,8 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
       <c r="I15" s="2"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -1028,9 +1007,8 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -1042,9 +1020,8 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
@@ -1056,9 +1033,8 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
@@ -1070,9 +1046,8 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
@@ -1084,9 +1059,8 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
       <c r="I20" s="2"/>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
@@ -1098,9 +1072,8 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
       <c r="I21" s="2"/>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
@@ -1112,9 +1085,8 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
       <c r="I22" s="2"/>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
@@ -1126,9 +1098,8 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
       <c r="I23" s="2"/>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
@@ -1140,9 +1111,8 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
       <c r="I24" s="2"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -1154,9 +1124,8 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
       <c r="I25" s="2"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -1168,9 +1137,8 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
       <c r="I26" s="2"/>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
@@ -1182,9 +1150,8 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
       <c r="I27" s="2"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
@@ -1196,9 +1163,8 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
       <c r="I28" s="2"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
@@ -1210,9 +1176,8 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
       <c r="I29" s="2"/>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
@@ -1224,9 +1189,8 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
       <c r="I30" s="2"/>
       <c r="J30" s="4"/>
       <c r="K30" s="2"/>
@@ -1238,9 +1202,8 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
       <c r="I31" s="2"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
@@ -1252,9 +1215,8 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
       <c r="I32" s="2"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
@@ -1266,9 +1228,8 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
       <c r="I33" s="2"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
@@ -1280,9 +1241,8 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
       <c r="I34" s="2"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
@@ -1294,9 +1254,8 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
       <c r="I35" s="2"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
@@ -1308,9 +1267,8 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
       <c r="I36" s="2"/>
       <c r="J36" s="4"/>
       <c r="K36" s="2"/>
@@ -1322,9 +1280,8 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
       <c r="I37" s="2"/>
       <c r="J37" s="4"/>
       <c r="K37" s="2"/>
@@ -1336,9 +1293,8 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
       <c r="I38" s="2"/>
       <c r="J38" s="4"/>
       <c r="K38" s="2"/>
@@ -1350,9 +1306,8 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
       <c r="I39" s="2"/>
       <c r="J39" s="4"/>
       <c r="K39" s="2"/>
@@ -1364,9 +1319,8 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
       <c r="I40" s="2"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
@@ -1378,9 +1332,8 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
       <c r="I41" s="2"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
@@ -1392,9 +1345,8 @@
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
       <c r="I42" s="2"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
@@ -1406,9 +1358,8 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
       <c r="I43" s="2"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
@@ -1420,9 +1371,8 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
       <c r="I44" s="2"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -1434,9 +1384,8 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
       <c r="I45" s="2"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
@@ -1448,9 +1397,8 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
       <c r="I46" s="2"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
@@ -1462,9 +1410,8 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
       <c r="I47" s="2"/>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
@@ -1476,9 +1423,8 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
       <c r="I48" s="2"/>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
@@ -1490,9 +1436,8 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
       <c r="I49" s="2"/>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
@@ -1504,9 +1449,8 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
       <c r="I50" s="2"/>
       <c r="J50" s="4"/>
       <c r="K50" s="2"/>
@@ -1518,9 +1462,8 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
       <c r="I51" s="2"/>
       <c r="J51" s="4"/>
       <c r="K51" s="2"/>
@@ -1532,9 +1475,8 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
       <c r="I52" s="2"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
@@ -1546,9 +1488,8 @@
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
       <c r="I53" s="2"/>
       <c r="J53" s="4"/>
       <c r="K53" s="2"/>
@@ -1560,9 +1501,8 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
       <c r="I54" s="2"/>
       <c r="J54" s="4"/>
       <c r="K54" s="2"/>
@@ -1574,9 +1514,8 @@
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
       <c r="I55" s="2"/>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
@@ -1588,9 +1527,8 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
       <c r="I56" s="2"/>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
@@ -1602,9 +1540,8 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
       <c r="I57" s="2"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
@@ -1616,9 +1553,8 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
       <c r="I58" s="2"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
@@ -1630,9 +1566,8 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
       <c r="I59" s="2"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
@@ -1644,9 +1579,8 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
       <c r="I60" s="2"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
@@ -1658,9 +1592,8 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
       <c r="I61" s="2"/>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
@@ -1672,9 +1605,8 @@
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
       <c r="I62" s="2"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
@@ -1686,9 +1618,8 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
       <c r="I63" s="2"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
@@ -1700,9 +1631,8 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
       <c r="I64" s="2"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
@@ -1714,9 +1644,8 @@
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
       <c r="I65" s="2"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -1728,9 +1657,8 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
       <c r="I66" s="2"/>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
@@ -1742,9 +1670,8 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
       <c r="I67" s="2"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -1756,9 +1683,8 @@
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
       <c r="I68" s="2"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
@@ -1770,9 +1696,8 @@
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
       <c r="I69" s="2"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
@@ -1784,9 +1709,8 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
       <c r="I70" s="2"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
@@ -1798,9 +1722,8 @@
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
       <c r="I71" s="2"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
@@ -1812,9 +1735,8 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
       <c r="I72" s="2"/>
       <c r="J72" s="4"/>
       <c r="K72" s="2"/>
@@ -1826,9 +1748,8 @@
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
       <c r="I73" s="2"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
@@ -1840,9 +1761,8 @@
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
       <c r="I74" s="2"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
@@ -1854,9 +1774,8 @@
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
       <c r="I75" s="2"/>
       <c r="J75" s="4"/>
       <c r="K75" s="2"/>
@@ -1868,9 +1787,8 @@
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
       <c r="I76" s="2"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
@@ -1882,9 +1800,8 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
       <c r="I77" s="2"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
@@ -1896,9 +1813,8 @@
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
       <c r="I78" s="2"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
@@ -1910,9 +1826,8 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
       <c r="I79" s="2"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -1924,9 +1839,8 @@
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
       <c r="I80" s="2"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
@@ -1938,9 +1852,8 @@
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
       <c r="I81" s="2"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
@@ -1952,9 +1865,8 @@
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
       <c r="I82" s="2"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
@@ -1966,9 +1878,8 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
       <c r="I83" s="2"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
@@ -1980,9 +1891,8 @@
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
       <c r="I84" s="2"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
@@ -1994,9 +1904,8 @@
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
       <c r="I85" s="2"/>
       <c r="J85" s="4"/>
       <c r="K85" s="2"/>
@@ -2008,9 +1917,8 @@
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
       <c r="I86" s="2"/>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
@@ -2022,9 +1930,8 @@
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="9"/>
       <c r="I87" s="2"/>
       <c r="J87" s="4"/>
       <c r="K87" s="2"/>
@@ -2036,9 +1943,8 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
       <c r="I88" s="2"/>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
@@ -2050,9 +1956,8 @@
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
       <c r="I89" s="2"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
@@ -2064,9 +1969,8 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
       <c r="I90" s="2"/>
       <c r="J90" s="4"/>
       <c r="K90" s="2"/>
@@ -2078,9 +1982,8 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
       <c r="I91" s="2"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -2092,9 +1995,8 @@
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
       <c r="I92" s="2"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
@@ -2106,9 +2008,8 @@
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="9"/>
       <c r="I93" s="2"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
@@ -2120,9 +2021,8 @@
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
       <c r="I94" s="2"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -2134,9 +2034,8 @@
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
       <c r="I95" s="2"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
@@ -2148,9 +2047,8 @@
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
       <c r="I96" s="2"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -2162,9 +2060,8 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
       <c r="I97" s="2"/>
       <c r="J97" s="4"/>
       <c r="K97" s="2"/>
@@ -2176,9 +2073,8 @@
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="10"/>
-      <c r="H98" s="10"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
       <c r="I98" s="2"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
@@ -2190,9 +2086,8 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
       <c r="I99" s="2"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -2204,9 +2099,8 @@
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
       <c r="I100" s="2"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -2218,9 +2112,8 @@
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
       <c r="I101" s="2"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -2232,9 +2125,8 @@
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="2"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="10"/>
-      <c r="H102" s="10"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
       <c r="I102" s="2"/>
       <c r="J102" s="4"/>
       <c r="K102" s="2"/>
@@ -2246,9 +2138,8 @@
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="10"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
       <c r="I103" s="2"/>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -2260,9 +2151,8 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9"/>
       <c r="I104" s="2"/>
       <c r="J104" s="4"/>
       <c r="K104" s="2"/>
@@ -2274,9 +2164,8 @@
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="2"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="10"/>
-      <c r="H105" s="10"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="9"/>
       <c r="I105" s="2"/>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -2288,9 +2177,8 @@
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="2"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="10"/>
-      <c r="H106" s="10"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
       <c r="I106" s="2"/>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -2302,9 +2190,8 @@
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="2"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
       <c r="I107" s="2"/>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -2316,9 +2203,8 @@
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="2"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
       <c r="I108" s="2"/>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -2330,9 +2216,8 @@
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="2"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
       <c r="I109" s="2"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
@@ -2344,9 +2229,8 @@
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="2"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
       <c r="I110" s="2"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -2358,9 +2242,8 @@
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="2"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
       <c r="I111" s="2"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -2372,9 +2255,8 @@
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="2"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
       <c r="I112" s="2"/>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -2386,9 +2268,8 @@
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="2"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
       <c r="I113" s="2"/>
       <c r="J113" s="4"/>
       <c r="K113" s="2"/>
@@ -2400,9 +2281,8 @@
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="2"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
       <c r="I114" s="2"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -2414,9 +2294,8 @@
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="2"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="10"/>
-      <c r="H115" s="10"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="9"/>
       <c r="I115" s="2"/>
       <c r="J115" s="4"/>
       <c r="K115" s="2"/>
@@ -2428,9 +2307,8 @@
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="2"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="10"/>
-      <c r="H116" s="10"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
       <c r="I116" s="2"/>
       <c r="J116" s="4"/>
       <c r="K116" s="2"/>
@@ -2442,9 +2320,8 @@
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="2"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="10"/>
-      <c r="H117" s="10"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="9"/>
       <c r="I117" s="2"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
@@ -2456,9 +2333,8 @@
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="2"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="10"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
       <c r="I118" s="2"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
@@ -2470,9 +2346,8 @@
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="2"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="10"/>
-      <c r="H119" s="10"/>
+      <c r="G119" s="9"/>
+      <c r="H119" s="9"/>
       <c r="I119" s="2"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
@@ -2484,9 +2359,8 @@
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="2"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="10"/>
-      <c r="H120" s="10"/>
+      <c r="G120" s="9"/>
+      <c r="H120" s="9"/>
       <c r="I120" s="2"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
@@ -2498,9 +2372,8 @@
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="2"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="10"/>
-      <c r="H121" s="10"/>
+      <c r="G121" s="9"/>
+      <c r="H121" s="9"/>
       <c r="I121" s="2"/>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
@@ -2512,9 +2385,8 @@
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="2"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="10"/>
-      <c r="H122" s="10"/>
+      <c r="G122" s="9"/>
+      <c r="H122" s="9"/>
       <c r="I122" s="2"/>
       <c r="J122" s="4"/>
       <c r="K122" s="2"/>
@@ -2526,9 +2398,8 @@
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="2"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="10"/>
-      <c r="H123" s="10"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
       <c r="I123" s="2"/>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
@@ -2540,9 +2411,8 @@
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="2"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="10"/>
-      <c r="H124" s="10"/>
+      <c r="G124" s="9"/>
+      <c r="H124" s="9"/>
       <c r="I124" s="2"/>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
@@ -2554,9 +2424,8 @@
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="2"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="10"/>
-      <c r="H125" s="10"/>
+      <c r="G125" s="9"/>
+      <c r="H125" s="9"/>
       <c r="I125" s="2"/>
       <c r="J125" s="4"/>
       <c r="K125" s="2"/>
@@ -2568,9 +2437,8 @@
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="2"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="10"/>
-      <c r="H126" s="10"/>
+      <c r="G126" s="9"/>
+      <c r="H126" s="9"/>
       <c r="I126" s="2"/>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
@@ -2582,9 +2450,8 @@
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="2"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="10"/>
-      <c r="H127" s="10"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="9"/>
       <c r="I127" s="2"/>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
@@ -2596,9 +2463,8 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="2"/>
-      <c r="F128" s="3"/>
-      <c r="G128" s="10"/>
-      <c r="H128" s="10"/>
+      <c r="G128" s="9"/>
+      <c r="H128" s="9"/>
       <c r="I128" s="2"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
@@ -2610,9 +2476,8 @@
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="2"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="10"/>
-      <c r="H129" s="10"/>
+      <c r="G129" s="9"/>
+      <c r="H129" s="9"/>
       <c r="I129" s="2"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -2624,9 +2489,8 @@
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="2"/>
-      <c r="F130" s="3"/>
-      <c r="G130" s="10"/>
-      <c r="H130" s="10"/>
+      <c r="G130" s="9"/>
+      <c r="H130" s="9"/>
       <c r="I130" s="2"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
@@ -2638,9 +2502,8 @@
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="2"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="10"/>
-      <c r="H131" s="10"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9"/>
       <c r="I131" s="2"/>
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
@@ -2652,9 +2515,8 @@
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="2"/>
-      <c r="F132" s="3"/>
-      <c r="G132" s="10"/>
-      <c r="H132" s="10"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="9"/>
       <c r="I132" s="2"/>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
@@ -2666,9 +2528,8 @@
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="2"/>
-      <c r="F133" s="3"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10"/>
+      <c r="G133" s="9"/>
+      <c r="H133" s="9"/>
       <c r="I133" s="2"/>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
@@ -2680,9 +2541,8 @@
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="2"/>
-      <c r="F134" s="3"/>
-      <c r="G134" s="10"/>
-      <c r="H134" s="10"/>
+      <c r="G134" s="9"/>
+      <c r="H134" s="9"/>
       <c r="I134" s="2"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
@@ -2694,9 +2554,8 @@
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="2"/>
-      <c r="F135" s="3"/>
-      <c r="G135" s="10"/>
-      <c r="H135" s="10"/>
+      <c r="G135" s="9"/>
+      <c r="H135" s="9"/>
       <c r="I135" s="2"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
@@ -2708,9 +2567,8 @@
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="3"/>
-      <c r="G136" s="10"/>
-      <c r="H136" s="10"/>
+      <c r="G136" s="9"/>
+      <c r="H136" s="9"/>
       <c r="I136" s="2"/>
       <c r="J136" s="4"/>
       <c r="K136" s="2"/>
@@ -2722,9 +2580,8 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="2"/>
-      <c r="F137" s="3"/>
-      <c r="G137" s="10"/>
-      <c r="H137" s="10"/>
+      <c r="G137" s="9"/>
+      <c r="H137" s="9"/>
       <c r="I137" s="2"/>
       <c r="J137" s="4"/>
       <c r="K137" s="2"/>
@@ -2736,9 +2593,8 @@
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="2"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="10"/>
-      <c r="H138" s="10"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="9"/>
       <c r="I138" s="2"/>
       <c r="J138" s="4"/>
       <c r="K138" s="2"/>
@@ -2750,9 +2606,8 @@
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="2"/>
-      <c r="F139" s="3"/>
-      <c r="G139" s="10"/>
-      <c r="H139" s="10"/>
+      <c r="G139" s="9"/>
+      <c r="H139" s="9"/>
       <c r="I139" s="2"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -2764,9 +2619,8 @@
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="2"/>
-      <c r="F140" s="3"/>
-      <c r="G140" s="10"/>
-      <c r="H140" s="10"/>
+      <c r="G140" s="9"/>
+      <c r="H140" s="9"/>
       <c r="I140" s="2"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
@@ -2778,9 +2632,8 @@
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="2"/>
-      <c r="F141" s="3"/>
-      <c r="G141" s="10"/>
-      <c r="H141" s="10"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
       <c r="I141" s="2"/>
       <c r="J141" s="4"/>
       <c r="K141" s="2"/>
@@ -2792,9 +2645,8 @@
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="2"/>
-      <c r="F142" s="3"/>
-      <c r="G142" s="10"/>
-      <c r="H142" s="10"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
       <c r="I142" s="2"/>
       <c r="J142" s="4"/>
       <c r="K142" s="2"/>
@@ -2806,9 +2658,8 @@
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="2"/>
-      <c r="F143" s="3"/>
-      <c r="G143" s="10"/>
-      <c r="H143" s="10"/>
+      <c r="G143" s="9"/>
+      <c r="H143" s="9"/>
       <c r="I143" s="2"/>
       <c r="J143" s="4"/>
       <c r="K143" s="2"/>
@@ -2820,9 +2671,8 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="2"/>
-      <c r="F144" s="3"/>
-      <c r="G144" s="10"/>
-      <c r="H144" s="10"/>
+      <c r="G144" s="9"/>
+      <c r="H144" s="9"/>
       <c r="I144" s="2"/>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
@@ -2834,9 +2684,8 @@
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="2"/>
-      <c r="F145" s="3"/>
-      <c r="G145" s="10"/>
-      <c r="H145" s="10"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="9"/>
       <c r="I145" s="2"/>
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
@@ -2848,9 +2697,8 @@
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="2"/>
-      <c r="F146" s="3"/>
-      <c r="G146" s="10"/>
-      <c r="H146" s="10"/>
+      <c r="G146" s="9"/>
+      <c r="H146" s="9"/>
       <c r="I146" s="2"/>
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
@@ -2862,9 +2710,8 @@
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="2"/>
-      <c r="F147" s="3"/>
-      <c r="G147" s="10"/>
-      <c r="H147" s="10"/>
+      <c r="G147" s="9"/>
+      <c r="H147" s="9"/>
       <c r="I147" s="2"/>
       <c r="J147" s="4"/>
       <c r="K147" s="2"/>
@@ -2876,9 +2723,8 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="2"/>
-      <c r="F148" s="3"/>
-      <c r="G148" s="10"/>
-      <c r="H148" s="10"/>
+      <c r="G148" s="9"/>
+      <c r="H148" s="9"/>
       <c r="I148" s="2"/>
       <c r="J148" s="4"/>
       <c r="K148" s="2"/>
@@ -2890,9 +2736,8 @@
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="2"/>
-      <c r="F149" s="3"/>
-      <c r="G149" s="10"/>
-      <c r="H149" s="10"/>
+      <c r="G149" s="9"/>
+      <c r="H149" s="9"/>
       <c r="I149" s="2"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
@@ -2904,9 +2749,8 @@
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="2"/>
-      <c r="F150" s="3"/>
-      <c r="G150" s="10"/>
-      <c r="H150" s="10"/>
+      <c r="G150" s="9"/>
+      <c r="H150" s="9"/>
       <c r="I150" s="2"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
@@ -2918,9 +2762,8 @@
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="2"/>
-      <c r="F151" s="3"/>
-      <c r="G151" s="10"/>
-      <c r="H151" s="10"/>
+      <c r="G151" s="9"/>
+      <c r="H151" s="9"/>
       <c r="I151" s="2"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -2932,9 +2775,8 @@
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="2"/>
-      <c r="F152" s="3"/>
-      <c r="G152" s="10"/>
-      <c r="H152" s="10"/>
+      <c r="G152" s="9"/>
+      <c r="H152" s="9"/>
       <c r="I152" s="2"/>
       <c r="J152" s="4"/>
       <c r="K152" s="2"/>
@@ -2946,9 +2788,8 @@
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="2"/>
-      <c r="F153" s="3"/>
-      <c r="G153" s="10"/>
-      <c r="H153" s="10"/>
+      <c r="G153" s="9"/>
+      <c r="H153" s="9"/>
       <c r="I153" s="2"/>
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
@@ -2960,9 +2801,8 @@
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="2"/>
-      <c r="F154" s="3"/>
-      <c r="G154" s="10"/>
-      <c r="H154" s="10"/>
+      <c r="G154" s="9"/>
+      <c r="H154" s="9"/>
       <c r="I154" s="2"/>
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
@@ -2974,9 +2814,8 @@
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="2"/>
-      <c r="F155" s="3"/>
-      <c r="G155" s="10"/>
-      <c r="H155" s="10"/>
+      <c r="G155" s="9"/>
+      <c r="H155" s="9"/>
       <c r="I155" s="2"/>
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
@@ -2988,9 +2827,8 @@
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="2"/>
-      <c r="F156" s="3"/>
-      <c r="G156" s="10"/>
-      <c r="H156" s="10"/>
+      <c r="G156" s="9"/>
+      <c r="H156" s="9"/>
       <c r="I156" s="2"/>
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
@@ -3002,9 +2840,8 @@
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="2"/>
-      <c r="F157" s="3"/>
-      <c r="G157" s="10"/>
-      <c r="H157" s="10"/>
+      <c r="G157" s="9"/>
+      <c r="H157" s="9"/>
       <c r="I157" s="2"/>
       <c r="J157" s="4"/>
       <c r="K157" s="2"/>
@@ -3016,9 +2853,8 @@
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="2"/>
-      <c r="F158" s="3"/>
-      <c r="G158" s="10"/>
-      <c r="H158" s="10"/>
+      <c r="G158" s="9"/>
+      <c r="H158" s="9"/>
       <c r="I158" s="2"/>
       <c r="J158" s="4"/>
       <c r="K158" s="2"/>
@@ -3030,9 +2866,8 @@
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="2"/>
-      <c r="F159" s="3"/>
-      <c r="G159" s="10"/>
-      <c r="H159" s="10"/>
+      <c r="G159" s="9"/>
+      <c r="H159" s="9"/>
       <c r="I159" s="2"/>
       <c r="J159" s="4"/>
       <c r="K159" s="2"/>
@@ -3044,9 +2879,8 @@
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="2"/>
-      <c r="F160" s="3"/>
-      <c r="G160" s="10"/>
-      <c r="H160" s="10"/>
+      <c r="G160" s="9"/>
+      <c r="H160" s="9"/>
       <c r="I160" s="2"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -3058,9 +2892,8 @@
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="2"/>
-      <c r="F161" s="3"/>
-      <c r="G161" s="10"/>
-      <c r="H161" s="10"/>
+      <c r="G161" s="9"/>
+      <c r="H161" s="9"/>
       <c r="I161" s="2"/>
       <c r="J161" s="4"/>
       <c r="K161" s="2"/>
@@ -3072,9 +2905,8 @@
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="2"/>
-      <c r="F162" s="3"/>
-      <c r="G162" s="10"/>
-      <c r="H162" s="10"/>
+      <c r="G162" s="9"/>
+      <c r="H162" s="9"/>
       <c r="I162" s="2"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
@@ -3086,9 +2918,8 @@
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="2"/>
-      <c r="F163" s="3"/>
-      <c r="G163" s="10"/>
-      <c r="H163" s="10"/>
+      <c r="G163" s="9"/>
+      <c r="H163" s="9"/>
       <c r="I163" s="2"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
@@ -3100,9 +2931,8 @@
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="2"/>
-      <c r="F164" s="3"/>
-      <c r="G164" s="10"/>
-      <c r="H164" s="10"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="9"/>
       <c r="I164" s="2"/>
       <c r="J164" s="4"/>
       <c r="K164" s="2"/>
@@ -3114,9 +2944,8 @@
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="2"/>
-      <c r="F165" s="3"/>
-      <c r="G165" s="10"/>
-      <c r="H165" s="10"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="9"/>
       <c r="I165" s="2"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
@@ -3128,9 +2957,8 @@
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="2"/>
-      <c r="F166" s="3"/>
-      <c r="G166" s="10"/>
-      <c r="H166" s="10"/>
+      <c r="G166" s="9"/>
+      <c r="H166" s="9"/>
       <c r="I166" s="2"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
@@ -3142,9 +2970,8 @@
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="2"/>
-      <c r="F167" s="3"/>
-      <c r="G167" s="10"/>
-      <c r="H167" s="10"/>
+      <c r="G167" s="9"/>
+      <c r="H167" s="9"/>
       <c r="I167" s="2"/>
       <c r="J167" s="4"/>
       <c r="K167" s="2"/>
@@ -3156,9 +2983,8 @@
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="2"/>
-      <c r="F168" s="3"/>
-      <c r="G168" s="10"/>
-      <c r="H168" s="10"/>
+      <c r="G168" s="9"/>
+      <c r="H168" s="9"/>
       <c r="I168" s="2"/>
       <c r="J168" s="4"/>
       <c r="K168" s="2"/>
@@ -3170,9 +2996,8 @@
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="2"/>
-      <c r="F169" s="3"/>
-      <c r="G169" s="10"/>
-      <c r="H169" s="10"/>
+      <c r="G169" s="9"/>
+      <c r="H169" s="9"/>
       <c r="I169" s="2"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
@@ -3184,9 +3009,8 @@
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="2"/>
-      <c r="F170" s="3"/>
-      <c r="G170" s="10"/>
-      <c r="H170" s="10"/>
+      <c r="G170" s="9"/>
+      <c r="H170" s="9"/>
       <c r="I170" s="2"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
@@ -3198,9 +3022,8 @@
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="2"/>
-      <c r="F171" s="3"/>
-      <c r="G171" s="10"/>
-      <c r="H171" s="10"/>
+      <c r="G171" s="9"/>
+      <c r="H171" s="9"/>
       <c r="I171" s="2"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -3212,9 +3035,8 @@
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="2"/>
-      <c r="F172" s="3"/>
-      <c r="G172" s="10"/>
-      <c r="H172" s="10"/>
+      <c r="G172" s="9"/>
+      <c r="H172" s="9"/>
       <c r="I172" s="2"/>
       <c r="J172" s="4"/>
       <c r="K172" s="2"/>
@@ -3226,9 +3048,8 @@
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="2"/>
-      <c r="F173" s="3"/>
-      <c r="G173" s="10"/>
-      <c r="H173" s="10"/>
+      <c r="G173" s="9"/>
+      <c r="H173" s="9"/>
       <c r="I173" s="2"/>
       <c r="J173" s="4"/>
       <c r="K173" s="2"/>
@@ -3240,9 +3061,8 @@
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="2"/>
-      <c r="F174" s="3"/>
-      <c r="G174" s="10"/>
-      <c r="H174" s="10"/>
+      <c r="G174" s="9"/>
+      <c r="H174" s="9"/>
       <c r="I174" s="2"/>
       <c r="J174" s="4"/>
       <c r="K174" s="2"/>
@@ -3254,9 +3074,8 @@
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="2"/>
-      <c r="F175" s="3"/>
-      <c r="G175" s="10"/>
-      <c r="H175" s="10"/>
+      <c r="G175" s="9"/>
+      <c r="H175" s="9"/>
       <c r="I175" s="2"/>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
@@ -3268,9 +3087,8 @@
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="2"/>
-      <c r="F176" s="3"/>
-      <c r="G176" s="10"/>
-      <c r="H176" s="10"/>
+      <c r="G176" s="9"/>
+      <c r="H176" s="9"/>
       <c r="I176" s="2"/>
       <c r="J176" s="4"/>
       <c r="K176" s="2"/>
@@ -3282,9 +3100,8 @@
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="2"/>
-      <c r="F177" s="3"/>
-      <c r="G177" s="10"/>
-      <c r="H177" s="10"/>
+      <c r="G177" s="9"/>
+      <c r="H177" s="9"/>
       <c r="I177" s="2"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
@@ -3296,9 +3113,8 @@
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="2"/>
-      <c r="F178" s="3"/>
-      <c r="G178" s="10"/>
-      <c r="H178" s="10"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="9"/>
       <c r="I178" s="2"/>
       <c r="J178" s="4"/>
       <c r="K178" s="2"/>
@@ -3310,9 +3126,8 @@
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="2"/>
-      <c r="F179" s="3"/>
-      <c r="G179" s="10"/>
-      <c r="H179" s="10"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="9"/>
       <c r="I179" s="2"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -3324,9 +3139,8 @@
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="2"/>
-      <c r="F180" s="3"/>
-      <c r="G180" s="10"/>
-      <c r="H180" s="10"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9"/>
       <c r="I180" s="2"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -3338,9 +3152,8 @@
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="2"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="10"/>
-      <c r="H181" s="10"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="9"/>
       <c r="I181" s="2"/>
       <c r="J181" s="4"/>
       <c r="K181" s="2"/>
@@ -3352,9 +3165,8 @@
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="2"/>
-      <c r="F182" s="3"/>
-      <c r="G182" s="10"/>
-      <c r="H182" s="10"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="9"/>
       <c r="I182" s="2"/>
       <c r="J182" s="4"/>
       <c r="K182" s="2"/>
@@ -3366,9 +3178,8 @@
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="2"/>
-      <c r="F183" s="3"/>
-      <c r="G183" s="10"/>
-      <c r="H183" s="10"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="9"/>
       <c r="I183" s="2"/>
       <c r="J183" s="4"/>
       <c r="K183" s="2"/>
@@ -3380,9 +3191,8 @@
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="2"/>
-      <c r="F184" s="3"/>
-      <c r="G184" s="10"/>
-      <c r="H184" s="10"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="9"/>
       <c r="I184" s="2"/>
       <c r="J184" s="4"/>
       <c r="K184" s="2"/>
@@ -3394,9 +3204,8 @@
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="2"/>
-      <c r="F185" s="3"/>
-      <c r="G185" s="10"/>
-      <c r="H185" s="10"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="9"/>
       <c r="I185" s="2"/>
       <c r="J185" s="4"/>
       <c r="K185" s="2"/>
@@ -3408,9 +3217,8 @@
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="2"/>
-      <c r="F186" s="3"/>
-      <c r="G186" s="10"/>
-      <c r="H186" s="10"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9"/>
       <c r="I186" s="2"/>
       <c r="J186" s="4"/>
       <c r="K186" s="2"/>
@@ -3422,9 +3230,8 @@
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="2"/>
-      <c r="F187" s="3"/>
-      <c r="G187" s="10"/>
-      <c r="H187" s="10"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9"/>
       <c r="I187" s="2"/>
       <c r="J187" s="4"/>
       <c r="K187" s="2"/>
@@ -3436,9 +3243,8 @@
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="2"/>
-      <c r="F188" s="3"/>
-      <c r="G188" s="10"/>
-      <c r="H188" s="10"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
       <c r="I188" s="2"/>
       <c r="J188" s="4"/>
       <c r="K188" s="2"/>
@@ -3450,9 +3256,8 @@
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="2"/>
-      <c r="F189" s="3"/>
-      <c r="G189" s="10"/>
-      <c r="H189" s="10"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9"/>
       <c r="I189" s="2"/>
       <c r="J189" s="4"/>
       <c r="K189" s="2"/>
@@ -3464,9 +3269,8 @@
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="2"/>
-      <c r="F190" s="3"/>
-      <c r="G190" s="10"/>
-      <c r="H190" s="10"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9"/>
       <c r="I190" s="2"/>
       <c r="J190" s="4"/>
       <c r="K190" s="2"/>
@@ -3478,9 +3282,8 @@
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="2"/>
-      <c r="F191" s="3"/>
-      <c r="G191" s="10"/>
-      <c r="H191" s="10"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="9"/>
       <c r="I191" s="2"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -3492,9 +3295,8 @@
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="2"/>
-      <c r="F192" s="3"/>
-      <c r="G192" s="10"/>
-      <c r="H192" s="10"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9"/>
       <c r="I192" s="2"/>
       <c r="J192" s="4"/>
       <c r="K192" s="2"/>
@@ -3506,9 +3308,8 @@
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="2"/>
-      <c r="F193" s="3"/>
-      <c r="G193" s="10"/>
-      <c r="H193" s="10"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="9"/>
       <c r="I193" s="2"/>
       <c r="J193" s="4"/>
       <c r="K193" s="2"/>
@@ -3520,9 +3321,8 @@
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="2"/>
-      <c r="F194" s="3"/>
-      <c r="G194" s="10"/>
-      <c r="H194" s="10"/>
+      <c r="G194" s="9"/>
+      <c r="H194" s="9"/>
       <c r="I194" s="2"/>
       <c r="J194" s="4"/>
       <c r="K194" s="2"/>
@@ -3534,9 +3334,8 @@
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="2"/>
-      <c r="F195" s="3"/>
-      <c r="G195" s="10"/>
-      <c r="H195" s="10"/>
+      <c r="G195" s="9"/>
+      <c r="H195" s="9"/>
       <c r="I195" s="2"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -3548,9 +3347,8 @@
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="2"/>
-      <c r="F196" s="3"/>
-      <c r="G196" s="10"/>
-      <c r="H196" s="10"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9"/>
       <c r="I196" s="2"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
@@ -3562,9 +3360,8 @@
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="2"/>
-      <c r="F197" s="3"/>
-      <c r="G197" s="10"/>
-      <c r="H197" s="10"/>
+      <c r="G197" s="9"/>
+      <c r="H197" s="9"/>
       <c r="I197" s="2"/>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
@@ -3576,9 +3373,8 @@
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="2"/>
-      <c r="F198" s="3"/>
-      <c r="G198" s="10"/>
-      <c r="H198" s="10"/>
+      <c r="G198" s="9"/>
+      <c r="H198" s="9"/>
       <c r="I198" s="2"/>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
@@ -3590,9 +3386,8 @@
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="2"/>
-      <c r="F199" s="3"/>
-      <c r="G199" s="10"/>
-      <c r="H199" s="10"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="9"/>
       <c r="I199" s="2"/>
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
@@ -3604,9 +3399,8 @@
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="2"/>
-      <c r="F200" s="3"/>
-      <c r="G200" s="10"/>
-      <c r="H200" s="10"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
       <c r="I200" s="2"/>
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
@@ -3618,9 +3412,8 @@
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="2"/>
-      <c r="F201" s="3"/>
-      <c r="G201" s="10"/>
-      <c r="H201" s="10"/>
+      <c r="G201" s="9"/>
+      <c r="H201" s="9"/>
       <c r="I201" s="2"/>
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
@@ -3632,9 +3425,8 @@
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="2"/>
-      <c r="F202" s="3"/>
-      <c r="G202" s="10"/>
-      <c r="H202" s="10"/>
+      <c r="G202" s="9"/>
+      <c r="H202" s="9"/>
       <c r="I202" s="2"/>
       <c r="J202" s="4"/>
       <c r="K202" s="2"/>
@@ -3643,16 +3435,16 @@
   </sheetData>
   <autoFilter ref="A11:L202" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="E8:L8"/>
     <mergeCell ref="E9:L9"/>
     <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.45" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
